--- a/AAII_Financials/Quarterly/IDCBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IDCBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="92">
   <si>
     <t>IDCBY</t>
   </si>
@@ -656,74 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -769,8 +772,11 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +822,11 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +872,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -882,8 +894,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -929,8 +942,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -976,8 +992,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1023,8 +1042,11 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1070,8 +1092,11 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1086,8 +1111,9 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1133,8 +1159,11 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1180,8 +1209,11 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1199,8 +1231,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1246,8 +1279,11 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1293,8 +1329,11 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1340,8 +1379,11 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1387,8 +1429,11 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1434,8 +1479,11 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1481,8 +1529,11 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1528,8 +1579,11 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1575,8 +1629,11 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1622,8 +1679,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1669,8 +1729,11 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1716,8 +1779,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1763,8 +1829,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1810,8 +1879,11 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1857,8 +1929,11 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1904,8 +1979,11 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1951,60 +2029,66 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2022,8 +2106,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2041,431 +2126,459 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>140493200</v>
+      </c>
+      <c r="E41" s="3">
         <v>292391900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>190950600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>287154500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>140194600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>388937500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>163410800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>432605600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>189933100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>546854000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>228816500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>453848800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>192450400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>419035800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>170648500</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>305695100</v>
+      </c>
+      <c r="E42" s="3">
         <v>289647100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>206951100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>248671300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>391565600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>376227100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>306333200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>294812300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>247247100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>446359400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>262353000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>366016000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>395860100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>308953900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>213561900</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>88452900</v>
+      </c>
+      <c r="E43" s="3">
         <v>180323000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>97347600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>170862200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>80973900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>166094400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>67447400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>194899300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>78734500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>171443700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>72339300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>145942200</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q43" s="3">
         <v>184306500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>86764600</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E44" s="3">
+      <c r="D44" s="3">
+        <v>440600</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>453600</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3">
         <v>461900</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>440100</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3">
         <v>443500</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3">
         <v>477500</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3">
         <v>862200</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q44" s="3">
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R44" s="3">
         <v>493700</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3">
+        <v>97631500</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3">
         <v>61567500</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3">
         <v>56433900</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
         <v>41081400</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>37966800</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>32585700</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3">
         <v>37443200</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R45" s="3">
         <v>30426100</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1038447300</v>
+      </c>
+      <c r="E46" s="3">
         <v>962767000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>938116500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>901619600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1012200200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1027170100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>939701600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1024071900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>923012300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1164657000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>996069900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1028160900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1012984700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1015700100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>885782500</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2660791900</v>
+      </c>
+      <c r="E47" s="3">
         <v>2456520700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2347718900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2184770500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2089686600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1947679500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1865565100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1790022400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1726998900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1582858500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1624694600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1486840300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1506856000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1487443400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1486613000</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>44976700</v>
+      </c>
+      <c r="E48" s="3">
         <v>41475800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>45291100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>41867900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>45377200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>41646500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>44714400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>41713500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>44529300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>40977600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>46094300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>40788000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>45882300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>42044800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>47359800</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>4660100</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>4620300</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>4610100</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>4538200</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>3206900</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>3300700</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>3318300</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
       <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
         <v>3441100</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2511,8 +2624,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2558,55 +2674,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>58276000</v>
+      </c>
+      <c r="E52" s="3">
         <v>140236200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>55411900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>112022300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>45639900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>92213300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>46460500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>128067700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>54405700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>101556300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>46269900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>86908000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>53520500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>84492700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>37349500</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2652,55 +2774,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8401630100</v>
+      </c>
+      <c r="E54" s="3">
         <v>8086030100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7645798500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7418448800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7303097700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7103568500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6688735000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6893970300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6483718800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6592345000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6303442300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6096376800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6021483700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6119183500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5742931300</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2718,8 +2846,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2737,290 +2866,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6557785600</v>
+      </c>
+      <c r="E57" s="3">
         <v>6449277600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5982825300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5942255500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5777833600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5697557100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5303063500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5541970100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5167981400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5417085900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5106264100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5069737400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4921899700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5099389200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4705274900</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>572933700</v>
+      </c>
+      <c r="E58" s="3">
         <v>487194000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>484465100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>344972300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>362782300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>296796700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>338143200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>261426300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>351434700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>242013200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>262629100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>114252100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>227942700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>109089300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>195384400</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4734900</v>
+      </c>
+      <c r="E59" s="3">
         <v>4835400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7462300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4805500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11509700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2464800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11393500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4918200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>18589800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4032700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8930000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7831600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>21094000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10113600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12408100</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7207714600</v>
+      </c>
+      <c r="E60" s="3">
         <v>7006215200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6560826200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6361845700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6234357200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6068361300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5742553900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5882268700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5616661000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5732599000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5462503300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5261217300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5244378600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5284715400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4987792900</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>379064200</v>
+      </c>
+      <c r="E61" s="3">
         <v>272930400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>320713000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>330726500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>366194100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>340498600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>281509400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>271963800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>222309000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>201866400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>196578100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>198132100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>165282900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>186361100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>135224600</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>172798100</v>
+      </c>
+      <c r="E62" s="3">
         <v>174629000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>152544200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>135778700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>123958800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>134357600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>117816600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>179867000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>112330300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>120335300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>111208500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>132639300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>115340100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>123099600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>109650600</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3066,8 +3214,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3113,8 +3264,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3160,55 +3314,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7760385800</v>
+      </c>
+      <c r="E66" s="3">
         <v>7454522700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7035020700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6829368200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6725349000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6543956300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6142466900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6334803200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5951923800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6055454900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5770845900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5592597200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5525583100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5594876100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5233243500</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3226,8 +3386,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3273,8 +3434,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3320,55 +3484,61 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>16918900</v>
+      </c>
+      <c r="E70" s="3">
         <v>16662400</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>16431300</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>16143200</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>18790900</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>18550800</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>18442500</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>19190800</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>18524300</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>18643300</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>18984000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>18448900</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>18561600</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>19596800</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>19517200</v>
       </c>
     </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3414,55 +3584,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>508107700</v>
+      </c>
+      <c r="E72" s="3">
         <v>328558700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>477843000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>311299900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>446581600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>288996800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>423787500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>293529300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>407284900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>276780300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>409265800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>263135800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>375479500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>270909000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>385801900</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3508,8 +3684,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3555,8 +3734,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3602,55 +3784,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>620078200</v>
+      </c>
+      <c r="E76" s="3">
         <v>610732200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>590376900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>569375800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>555582000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>537671100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>525438300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>536954700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>510384300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>515609400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>510834000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>482612300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>474523300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>501771500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>487371000</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3696,60 +3884,66 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3795,8 +3989,11 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3814,55 +4011,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>981700</v>
+      </c>
+      <c r="E83" s="3">
         <v>963400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1135900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>958400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1025200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>981800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1062900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1039000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1092600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1063200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1160500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1045400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1142100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1136500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1486000</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3908,8 +4109,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3955,8 +4159,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4002,8 +4209,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4049,8 +4259,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4096,55 +4309,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-103603500</v>
+      </c>
+      <c r="E89" s="3">
         <v>7023700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>37732300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>45771200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-99417600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-92021900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-32255800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>74736800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-61251400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-19008900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-14223700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8467100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-146700200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-147628500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-43285400</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4162,55 +4381,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1226900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-759000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3125900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1956000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-985000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-845300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1766800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2667800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-619200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-995500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1656900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-630400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1659100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-410500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>1331000</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4256,8 +4479,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4303,55 +4529,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-99794300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-112576300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-62803800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-112461400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-53063700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-109906200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-46880700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-48636800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-80941900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-27688000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-27640400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-32759900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-19033000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-46408300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-33656100</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4369,55 +4601,59 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3">
         <v>4058800</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3">
         <v>7724900</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3">
         <v>7043200</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K96" s="3">
         <v>15046100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>389200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>115500</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3">
         <v>14326500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>389900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>117300</v>
       </c>
-      <c r="Q96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4463,8 +4699,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4510,8 +4749,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4557,145 +4799,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>183983600</v>
+      </c>
+      <c r="E100" s="3">
         <v>143322400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11106200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>12754500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>98591800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>275107600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-25606300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>97396800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-107095300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>217491900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-33828900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>61982300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>181096800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>333922000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-23389500</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-608800</v>
+      </c>
+      <c r="E101" s="3">
         <v>123200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2797600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1982200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-121000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>779200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2692200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-44700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>6482400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1355200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1776400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>6900000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4706200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1185800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1879700</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-20970600</v>
+      </c>
+      <c r="E102" s="3">
         <v>35917000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-39360100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-54444300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-54498300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>73302700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-101945200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>121514600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-249409700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>171574100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-78385100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>37644800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>21845900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>138530000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-102107400</v>
       </c>
     </row>
